--- a/artfynd/S 2110-2023 artfynd.xlsx
+++ b/artfynd/S 2110-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY170"/>
+  <dimension ref="A1:AZ170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7257270</t>
         </is>
       </c>
     </row>
@@ -1017,6 +1032,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61651030</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542647</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542643</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542644</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542645</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542669</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542641</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542651</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542660</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542661</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2084,6 +2154,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542653</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2181,6 +2256,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542642</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2278,6 +2358,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542657</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160414</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2500,6 +2590,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160423</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2611,6 +2706,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160418</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2722,6 +2822,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160420</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2833,6 +2938,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160421</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2944,6 +3054,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160422</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3055,6 +3170,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160426</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3166,6 +3286,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160427</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3277,6 +3402,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160430</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3393,6 +3523,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160433</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3504,6 +3639,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160668</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3615,6 +3755,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160670</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3731,6 +3876,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160674</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3842,6 +3992,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160678</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3953,6 +4108,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160679</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4050,6 +4210,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542295</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4147,6 +4312,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542674</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4244,6 +4414,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542676</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4341,6 +4516,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542678</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4442,6 +4622,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120474774</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4547,6 +4732,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7257273</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4657,6 +4847,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/467182</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4763,6 +4958,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/468164</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4875,6 +5075,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70951808</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4972,6 +5177,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542666</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5069,6 +5279,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542668</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5166,6 +5381,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542667</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5263,6 +5483,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542670</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5360,6 +5585,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542658</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5457,6 +5687,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542673</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5554,6 +5789,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542675</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5651,6 +5891,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542343</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5748,6 +5993,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542356</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5845,6 +6095,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542303</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5942,6 +6197,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542336</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6039,6 +6299,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542342</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6136,6 +6401,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542354</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6233,6 +6503,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542366</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6330,6 +6605,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542301</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6427,6 +6707,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542352</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6524,6 +6809,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542358</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6621,6 +6911,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542367</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6718,6 +7013,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542380</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6815,6 +7115,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542258</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6912,6 +7217,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542260</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7009,6 +7319,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542270</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7106,6 +7421,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542273</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7203,6 +7523,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542293</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7300,6 +7625,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542302</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7397,6 +7727,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542308</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7494,6 +7829,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542332</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7591,6 +7931,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542339</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7688,6 +8033,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542359</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7785,6 +8135,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542364</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7894,6 +8249,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120444328</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7991,6 +8351,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542360</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8088,6 +8453,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542640</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8185,6 +8555,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542646</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8282,6 +8657,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542652</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8379,6 +8759,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542664</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8476,6 +8861,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542639</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8573,6 +8963,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542665</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8670,6 +9065,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542365</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8767,6 +9167,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542654</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8883,6 +9288,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542650</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8980,6 +9390,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1705223</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9077,6 +9492,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542265</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9174,6 +9594,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542268</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9271,6 +9696,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542272</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9368,6 +9798,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542278</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9465,6 +9900,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542307</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9562,6 +10002,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542313</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9659,6 +10104,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542321</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9756,6 +10206,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542329</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9853,6 +10308,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542331</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9950,6 +10410,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542341</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10047,6 +10512,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542349</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10144,6 +10614,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542363</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10241,6 +10716,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542345</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10372,6 +10852,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91000709</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10500,6 +10985,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128362292</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10628,6 +11118,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128362328</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10760,6 +11255,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128362414</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10869,6 +11369,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93192946</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10966,6 +11471,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542267</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11063,6 +11573,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542290</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11160,6 +11675,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542372</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11257,6 +11777,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542663</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11368,6 +11893,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2149260</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11474,6 +12004,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2154404</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11585,6 +12120,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2160011</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11682,6 +12222,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542281</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11779,6 +12324,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542309</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11876,6 +12426,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542335</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11973,6 +12528,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542361</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12084,6 +12644,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2701025</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12195,6 +12760,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3367737</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12306,6 +12876,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3378012</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12403,6 +12978,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542279</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12500,6 +13080,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542338</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12597,6 +13182,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542344</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12694,6 +13284,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542325</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12791,6 +13386,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542677</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12902,6 +13502,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4235115</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13011,6 +13616,11 @@
       <c r="AY122" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4237674</t>
         </is>
       </c>
     </row>
@@ -13122,6 +13732,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70952072</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13219,6 +13834,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542289</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13316,6 +13936,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542327</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13413,6 +14038,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542348</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13524,6 +14154,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5025026</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13635,6 +14270,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5045145</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13732,6 +14372,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542257</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13829,6 +14474,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542259</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13926,6 +14576,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542261</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14023,6 +14678,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542264</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14120,6 +14780,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542266</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14217,6 +14882,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542269</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14314,6 +14984,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542274</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14411,6 +15086,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542276</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14508,6 +15188,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542280</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14605,6 +15290,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542288</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14702,6 +15392,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542291</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14799,6 +15494,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542292</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14896,6 +15596,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542294</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14993,6 +15698,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542296</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15090,6 +15800,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542298</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15187,6 +15902,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542299</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15284,6 +16004,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542304</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15381,6 +16106,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542305</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15478,6 +16208,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542311</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15575,6 +16310,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542312</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15672,6 +16412,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542314</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15769,6 +16514,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542319</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15866,6 +16616,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542320</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15963,6 +16718,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542322</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16060,6 +16820,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542326</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16157,6 +16922,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542328</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16254,6 +17024,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542334</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16351,6 +17126,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542337</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16448,6 +17228,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542340</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16545,6 +17330,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542346</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16642,6 +17432,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542351</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16739,6 +17534,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542357</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16837,6 +17637,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542362</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16948,6 +17753,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5779774</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17066,6 +17876,11 @@
       <c r="AY163" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5791407</t>
         </is>
       </c>
     </row>
@@ -17177,6 +17992,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70952098</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17274,6 +18094,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542656</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17385,6 +18210,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5930213</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17482,6 +18312,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542655</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17579,6 +18414,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542671</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17676,6 +18516,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542353</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17773,8 +18618,184 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542370</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>